--- a/datastory/data/story_worksheet.xlsx
+++ b/datastory/data/story_worksheet.xlsx
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan the story before you write it.</t>
+          <t xml:space="preserve">A data story is planned long before it is written, and this is where the planning goes.</t>
         </is>
       </c>
     </row>

--- a/datastory/data/story_worksheet.xlsx
+++ b/datastory/data/story_worksheet.xlsx
@@ -1,32 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Elements" sheetId="1" r:id="rId1"/>
-    <sheet name="Steps" sheetId="2" r:id="rId2"/>
-    <sheet name="Fields" sheetId="3" r:id="rId3"/>
-    <sheet name="Options" sheetId="4" r:id="rId4"/>
-    <sheet name="Copy" sheetId="5" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elements" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -42,2762 +52,3161 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">element_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">letter</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">intro</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">order</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>element_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>letter</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>intro</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>order</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strategy</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Settle what the story is for, where it will live, who will tell it, and what falls inside its bounds, before any of it is written.</t>
-        </is>
-      </c>
-      <c r="E2">
+          <t>Settle what the story is for, where it will live, who will tell it, and what falls inside its bounds, before any of it is written.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">T</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">T</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Target Audience</t>
+          <t>Target Audience</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stories land with a narrow, well-defined audience rather than with "the public" or "policymakers," so name who you are speaking to and what they already know and care about.</t>
-        </is>
-      </c>
-      <c r="E3">
+          <t>Stories land with a narrow, well-defined audience rather than with "the public" or "policymakers," so name who you are speaking to and what they already know and care about.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
+          <t>O</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observations</t>
+          <t>Observations</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Let the data lead: state what they show, be open about where they came from and what could have bent them, and decide how much of the backstory this audience needs.</t>
-        </is>
-      </c>
-      <c r="E4">
+          <t>Let the data lead: state what they show, be open about where they came from and what could have bent them, and decide how much of the backstory this audience needs.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Representations</t>
+          <t>Representations</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Design the narrative and the illustration that carry the finding, with the people behind the data points, not the researcher, as the main characters.</t>
-        </is>
-      </c>
-      <c r="E5">
+          <t>Design the narrative and the illustration that carry the finding, with the people behind the data points, not the researcher, as the main characters.</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yield</t>
+          <t>Yield</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan how the story goes out and how you will know whether it moved anyone to act, because insights alone are not the harvest.</t>
-        </is>
-      </c>
-      <c r="E6">
+          <t>Plan how the story goes out and how you will know whether it moved anyone to act, because insights alone are not the harvest.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">step_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">element_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">order</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">label</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">help_text</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">link_label</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">link_url</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>step_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>element_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>help_text</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>link_label</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>link_url</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S1</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="C2">
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define the Objective</t>
+          <t>Define the Objective</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The point of view: the message, and the action the story is meant to inspire. The objectives listed are the common ones the Conference of State Court Administrators (2024) names for court communications.</t>
+          <t>The point of view: the message, and the action the story is meant to inspire. The objectives listed are the common ones the Conference of State Court Administrators (2024) names for court communications.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">S2</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="C3">
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Select the Format</t>
+          <t>Select the Format</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Formats differ in length, in how visual they are, and in how far they reach, and some communications come with a format already fixed.</t>
+          <t>Formats differ in length, in how visual they are, and in how far they reach, and some communications come with a format already fixed.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not sure? Open the format picker</t>
+          <t>Not sure? Open the format picker</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">../formatpicker/format_picker.html</t>
+          <t>../formatpicker/format_picker.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">S3</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="C4">
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identify the Reliable Narrator</t>
+          <t>Identify the Reliable Narrator</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audiences act more readily on a story from a credible, trustworthy narrator, but expertise alone does not carry it: a well-credentialed narrator with poor story logic fares worse than a non-expert with a sound one.</t>
+          <t>Audiences act more readily on a story from a credible, trustworthy narrator, but expertise alone does not carry it: a well-credentialed narrator with poor story logic fares worse than a non-expert with a sound one.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">S4</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="C5">
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Determine the Scope</t>
+          <t>Determine the Scope</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The boundaries of the story: its purpose, its themes, and the constraints it has to work within.</t>
+          <t>The boundaries of the story: its purpose, its themes, and the constraints it has to work within.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">T1</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">T</t>
-        </is>
-      </c>
-      <c r="C6">
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Specify the Audience</t>
+          <t>Specify the Audience</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broad, undefined audiences produce generalized messages and little action. Name the audience as narrowly as you honestly can.</t>
+          <t>Broad, undefined audiences produce generalized messages and little action. Name the audience as narrowly as you honestly can.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">T</t>
-        </is>
-      </c>
-      <c r="C7">
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Document their Expertise and Values</t>
+          <t>Document their Expertise and Values</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expertise sets how granular the data can be; interest and values decide whether the story engages at all. If you do not know these, find out before you draft.</t>
+          <t>Expertise sets how granular the data can be; interest and values decide whether the story engages at all. If you do not know these, find out before you draft.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">T3</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">T</t>
-        </is>
-      </c>
-      <c r="C8">
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Narrow the Audience into Subgroups</t>
+          <t>Narrow the Audience into Subgroups</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A story written for one subgroup can adapt its logic, emotion, and illustration to that group, which a story written for everyone cannot.</t>
+          <t>A story written for one subgroup can adapt its logic, emotion, and illustration to that group, which a story written for everyone cannot.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">O1</t>
+          <t>O1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C9">
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">State the Main Finding</t>
+          <t>State the Main Finding</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">One finding the data support, stated plainly. Let the data lead the story rather than choosing data to fit a storyline you already had.</t>
+          <t>One finding the data support, stated plainly. Let the data lead the story rather than choosing data to fit a storyline you already had.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">O2</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C10">
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Describe the Data Context and Biases</t>
+          <t>Describe the Data Context and Biases</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Document the data's context across its life cycle and describe it openly in the story, so biases such as sampling bias or cognitive bias do not steer it unnoticed.</t>
+          <t>Document the data's context across its life cycle and describe it openly in the story, so biases such as sampling bias or cognitive bias do not steer it unnoticed.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">O3</t>
+          <t>O3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">O</t>
-        </is>
-      </c>
-      <c r="C11">
+          <t>O</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decide the Supporting Details</t>
+          <t>Decide the Supporting Details</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enough detail to transfer the knowledge clearly, accurately, and reliably, but not so much that the audience loses interest; the right amount depends on the strategy and the audience.</t>
+          <t>Enough detail to transfer the knowledge clearly, accurately, and reliably, but not so much that the audience loses interest; the right amount depends on the strategy and the audience.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
-        </is>
-      </c>
-      <c r="C12">
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Draft the Narrative</t>
+          <t>Draft the Narrative</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">In data reporting the researcher is the protagonist and the arc follows the method; in data storytelling the subjects of the data points are the main characters, and the arc follows their journey. The context sets out the plot, the characters, and the current state.</t>
+          <t>In data reporting the researcher is the protagonist and the arc follows the method; in data storytelling the subjects of the data points are the main characters, and the arc follows their journey. The context sets out the plot, the characters, and the current state.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">R2</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
-        </is>
-      </c>
-      <c r="C13">
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consider the Challenge</t>
+          <t>Consider the Challenge</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Like a news hook, the challenge names the problem and creates tension or surprise; it is what sparks curiosity and connects to the audience's values.</t>
+          <t>Like a news hook, the challenge names the problem and creates tension or surprise; it is what sparks curiosity and connects to the audience's values.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">R3</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
-        </is>
-      </c>
-      <c r="C14">
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explain the Discovery</t>
+          <t>Explain the Discovery</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">At the peak of the arc, the discovery reveals the insight the story has been building toward, and the narrative then connects it to why it matters to this audience.</t>
+          <t>At the peak of the arc, the discovery reveals the insight the story has been building toward, and the narrative then connects it to why it matters to this audience.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">R4</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
-        </is>
-      </c>
-      <c r="C15">
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Create an Illustration</t>
+          <t>Create an Illustration</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Illustrations complement the narrative rather than replace it, and they need not be charts: a diagram, a table, or a personal story can carry an insight best.</t>
+          <t>Illustrations complement the narrative rather than replace it, and they need not be charts: a diagram, a table, or a personal story can carry an insight best.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Not sure? Open the display picker</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>../qualpicker/qual_picker.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="C16">
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conclude with a Call to Action</t>
+          <t>Conclude with a Call to Action</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">The call to action closes the narrative with some urgency and works best when it is proportional to the format and the audience. Sometimes it is less direct, and the best course is worked out with the audience.</t>
+          <t>The call to action closes the narrative with some urgency and works best when it is proportional to the format and the audience. Sometimes it is less direct, and the best course is worked out with the audience.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2</t>
+          <t>Y2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="C17">
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Advance the Dissemination Strategy</t>
+          <t>Advance the Dissemination Strategy</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan the channels ahead of time, and consider the practices that sustain a story: recurring themes or characters, timing it for when the audience is most ready, and tying it to the court's longer-term objectives.</t>
+          <t>Plan the channels ahead of time, and consider the practices that sustain a story: recurring themes or characters, timing it for when the audience is most ready, and tying it to the court's longer-term objectives.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y3</t>
+          <t>Y3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="C18">
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Measure the Response to the Call to Action</t>
+          <t>Measure the Response to the Call to Action</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether the story worked is measured by whether the audience acted, so define the specific behavior you hope to see and how you will measure it.</t>
+          <t>Whether the story worked is measured by whether the audience acted, so define the specific behavior you hope to see and how you will measure it.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">field_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">step_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">order</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">prompt</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">help_text</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">input_type</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">list_id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">placeholder</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>field_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>step_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>help_text</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>input_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>list_id</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">objective</t>
+          <t>objective</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">S1</t>
-        </is>
-      </c>
-      <c r="C2">
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which objective comes closest?</t>
+          <t>Which objective comes closest?</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">objectives</t>
+          <t>objectives</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">objective_mode</t>
+          <t>objective_mode</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">S1</t>
-        </is>
-      </c>
-      <c r="C3">
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Is the story meant to prompt action or to inform?</t>
+          <t>Is the story meant to prompt action or to inform?</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Action-focused stories carry heavy messaging and reveal information in a set order; informative ones carry less messaging and let the audience explore.</t>
+          <t>Action-focused stories carry heavy messaging and reveal information in a set order; informative ones carry less messaging and let the audience explore.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">objective_modes</t>
+          <t>objective_modes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">point_of_view</t>
+          <t>point_of_view</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">S1</t>
-        </is>
-      </c>
-      <c r="C4">
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">In a sentence or two, what should the audience think or do afterward?</t>
+          <t>In a sentence or two, what should the audience think or do afterward?</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">format</t>
+          <t>format</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">S2</t>
-        </is>
-      </c>
-      <c r="C5">
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which format?</t>
+          <t>Which format?</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">@formats</t>
+          <t>@formats</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">format_constraints</t>
+          <t>format_constraints</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">S2</t>
-        </is>
-      </c>
-      <c r="C6">
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Is anything about the format already decided for you?</t>
+          <t>Is anything about the format already decided for you?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">A required template, a page or time limit, a venue, a deadline.</t>
+          <t>A required template, a page or time limit, a venue, a deadline.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">narrator</t>
+          <t>narrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">S3</t>
-        </is>
-      </c>
-      <c r="C7">
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who will tell the story?</t>
+          <t>Who will tell the story?</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name and role</t>
+          <t>Name and role</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">credibility</t>
+          <t>credibility</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">S3</t>
-        </is>
-      </c>
-      <c r="C8">
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why will this audience trust them?</t>
+          <t>Why will this audience trust them?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credentials, stated experience, court examples, or a track record with this audience.</t>
+          <t>Credentials, stated experience, court examples, or a track record with this audience.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">scope_purpose</t>
+          <t>scope_purpose</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">S4</t>
-        </is>
-      </c>
-      <c r="C9">
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the purpose, and what is out of bounds?</t>
+          <t>What is the purpose, and what is out of bounds?</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">scope_themes</t>
+          <t>scope_themes</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">S4</t>
-        </is>
-      </c>
-      <c r="C10">
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which themes will it carry?</t>
+          <t>Which themes will it carry?</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">scope_constraints</t>
+          <t>scope_constraints</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">S4</t>
-        </is>
-      </c>
-      <c r="C11">
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">What constraints does it have to work within?</t>
+          <t>What constraints does it have to work within?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time, length, data availability, approvals.</t>
+          <t>Time, length, data availability, approvals.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">audience</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">T1</t>
-        </is>
-      </c>
-      <c r="C12">
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who, specifically, is the audience?</t>
+          <t>Who, specifically, is the audience?</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not "the public": which public?</t>
+          <t>Not "the public": which public?</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">audience_level</t>
+          <t>audience_level</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2</t>
-        </is>
-      </c>
-      <c r="C13">
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Where do they sit on the expertise ladder?</t>
+          <t>Where do they sit on the expertise ladder?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">These levels, novice through trustee or funder, come from dissemination science (Tabak and colleagues, 2013).</t>
+          <t>These levels, novice through trustee or funder, come from dissemination science (Tabak and colleagues, 2013).</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">@audiences</t>
+          <t>@audiences</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">court_expertise</t>
+          <t>court_expertise</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2</t>
-        </is>
-      </c>
-      <c r="C14">
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">How much do they know about court operations?</t>
+          <t>How much do they know about court operations?</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">low_high</t>
+          <t>low_high</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">data_literacy</t>
+          <t>data_literacy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2</t>
-        </is>
-      </c>
-      <c r="C15">
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">How comfortable are they with data?</t>
+          <t>How comfortable are they with data?</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">low_high</t>
+          <t>low_high</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">interest</t>
+          <t>interest</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2</t>
-        </is>
-      </c>
-      <c r="C16">
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">How interested are they in this topic already?</t>
+          <t>How interested are they in this topic already?</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">low_high</t>
+          <t>low_high</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">values</t>
+          <t>values</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">T2</t>
-        </is>
-      </c>
-      <c r="C17">
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">What do they value?</t>
+          <t>What do they value?</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">The core beliefs they will judge the story against.</t>
+          <t>The core beliefs they will judge the story against.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">subgroup</t>
+          <t>subgroup</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">T3</t>
-        </is>
-      </c>
-      <c r="C18">
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which subgroup is this story written for?</t>
+          <t>Which subgroup is this story written for?</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">subgroup_unknowns</t>
+          <t>subgroup_unknowns</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">T3</t>
-        </is>
-      </c>
-      <c r="C19">
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">What do you still need to learn about them, and how?</t>
+          <t>What do you still need to learn about them, and how?</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_finding</t>
+          <t>main_finding</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">O1</t>
-        </is>
-      </c>
-      <c r="C20">
+          <t>O1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the main finding?</t>
+          <t>What is the main finding?</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">data_context</t>
+          <t>data_context</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">O2</t>
-        </is>
-      </c>
-      <c r="C21">
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Where did the data come from, and what shaped them along the way?</t>
+          <t>Where did the data come from, and what shaped them along the way?</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">bias_types</t>
+          <t>bias_types</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">O2</t>
-        </is>
-      </c>
-      <c r="C22">
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which biases could be at work?</t>
+          <t>Which biases could be at work?</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">multi</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">biases</t>
+          <t>biases</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">bias_notes</t>
+          <t>bias_notes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">O2</t>
-        </is>
-      </c>
-      <c r="C23">
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">How will the story acknowledge them?</t>
+          <t>How will the story acknowledge them?</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_types</t>
+          <t>detail_types</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">O3</t>
-        </is>
-      </c>
-      <c r="C24">
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which supporting details will you include?</t>
+          <t>Which supporting details will you include?</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">multi</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_types</t>
+          <t>detail_types</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_level</t>
+          <t>detail_level</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">O3</t>
-        </is>
-      </c>
-      <c r="C25">
+          <t>O3</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">How much detail does this audience need?</t>
+          <t>How much detail does this audience need?</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_levels</t>
+          <t>detail_levels</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">narrative_arc</t>
+          <t>narrative_arc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1</t>
-        </is>
-      </c>
-      <c r="C26">
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which arc fits this audience?</t>
+          <t>Which arc fits this audience?</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">The research-method arc suits audiences who intend to replicate the work and need fine-grained detail.</t>
+          <t>The research-method arc suits audiences who intend to replicate the work and need fine-grained detail.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">arcs</t>
+          <t>arcs</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_character</t>
+          <t>main_character</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1</t>
-        </is>
-      </c>
-      <c r="C27">
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who is the main character?</t>
+          <t>Who is the main character?</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t>text</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whose journey does the data describe?</t>
+          <t>Whose journey does the data describe?</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">context</t>
+          <t>context</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1</t>
-        </is>
-      </c>
-      <c r="C28">
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the context: the plot, the characters, and the current state?</t>
+          <t>What is the context: the plot, the characters, and the current state?</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">challenge</t>
+          <t>challenge</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">R2</t>
-        </is>
-      </c>
-      <c r="C29">
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the challenge?</t>
+          <t>What is the challenge?</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">discovery</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">R3</t>
-        </is>
-      </c>
-      <c r="C30">
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the discovery?</t>
+          <t>What is the discovery?</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">relevance</t>
+          <t>relevance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">R3</t>
-        </is>
-      </c>
-      <c r="C31">
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why does it matter to this audience in particular?</t>
+          <t>Why does it matter to this audience in particular?</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_type</t>
+          <t>illustration_type</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">R4</t>
-        </is>
-      </c>
-      <c r="C32">
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">What kind of illustration?</t>
+          <t>What kind of illustration?</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_types</t>
+          <t>illustration_types</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_idea</t>
+          <t>illustration_idea</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">R4</t>
-        </is>
-      </c>
-      <c r="C33">
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Describe it.</t>
+          <t>Describe it.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_checks</t>
+          <t>illustration_checks</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">R4</t>
-        </is>
-      </c>
-      <c r="C34">
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Before it goes out, have you:</t>
+          <t>Before it goes out, have you:</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">multi</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_checks</t>
+          <t>illustration_checks</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">call_to_action</t>
+          <t>call_to_action</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1</t>
-        </is>
-      </c>
-      <c r="C35">
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the call to action?</t>
+          <t>What is the call to action?</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">cta_mode</t>
+          <t>cta_mode</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1</t>
-        </is>
-      </c>
-      <c r="C36">
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">How direct is it?</t>
+          <t>How direct is it?</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">select</t>
+          <t>select</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">cta_modes</t>
+          <t>cta_modes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2</t>
-        </is>
-      </c>
-      <c r="C37">
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Through which channels?</t>
+          <t>Through which channels?</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">multi</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels</t>
+          <t>channels</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels_other</t>
+          <t>channels_other</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2</t>
-        </is>
-      </c>
-      <c r="C38">
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any other channels, and when will it go out?</t>
+          <t>Any other channels, and when will it go out?</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">sustain</t>
+          <t>sustain</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y2</t>
-        </is>
-      </c>
-      <c r="C39">
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
         <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Which sustaining practices will you use?</t>
+          <t>Which sustaining practices will you use?</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">multi</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">sustain</t>
+          <t>sustain</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">outcome</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y3</t>
-        </is>
-      </c>
-      <c r="C40">
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">What specific audience behavior would show it worked?</t>
+          <t>What specific audience behavior would show it worked?</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">measure</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y3</t>
-        </is>
-      </c>
-      <c r="C41">
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">How will you measure it, and when?</t>
+          <t>How will you measure it, and when?</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">textarea</t>
+          <t>textarea</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">list_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">option</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">order</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>list_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>option</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>order</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">objectives</t>
+          <t>objectives</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Securing funding</t>
-        </is>
-      </c>
-      <c r="C2">
+          <t>Securing funding</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">objectives</t>
+          <t>objectives</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Influencing policy decisions</t>
-        </is>
-      </c>
-      <c r="C3">
+          <t>Influencing policy decisions</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">objectives</t>
+          <t>objectives</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enhancing engagement and collaboration</t>
-        </is>
-      </c>
-      <c r="C4">
+          <t>Enhancing engagement and collaboration</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">objectives</t>
+          <t>objectives</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Improving transparency and accountability</t>
-        </is>
-      </c>
-      <c r="C5">
+          <t>Improving transparency and accountability</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">objectives</t>
+          <t>objectives</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proactively sharing accurate information</t>
-        </is>
-      </c>
-      <c r="C6">
+          <t>Proactively sharing accurate information</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">objectives</t>
+          <t>objectives</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Something else</t>
-        </is>
-      </c>
-      <c r="C7">
+          <t>Something else</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">objective_modes</t>
+          <t>objective_modes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prompt action (author-driven, noninteractive)</t>
-        </is>
-      </c>
-      <c r="C8">
+          <t>Prompt action (author-driven, noninteractive)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">objective_modes</t>
+          <t>objective_modes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inform (audience-driven, interactive)</t>
-        </is>
-      </c>
-      <c r="C9">
+          <t>Inform (audience-driven, interactive)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">low_high</t>
+          <t>low_high</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
-        </is>
-      </c>
-      <c r="C10">
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">low_high</t>
+          <t>low_high</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moderate</t>
-        </is>
-      </c>
-      <c r="C11">
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">low_high</t>
+          <t>low_high</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="C12">
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">low_high</t>
+          <t>low_high</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not sure yet</t>
-        </is>
-      </c>
-      <c r="C13">
+          <t>Not sure yet</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">biases</t>
+          <t>biases</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sampling bias</t>
-        </is>
-      </c>
-      <c r="C14">
+          <t>Sampling bias</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">biases</t>
+          <t>biases</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cognitive bias</t>
-        </is>
-      </c>
-      <c r="C15">
+          <t>Cognitive bias</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">biases</t>
+          <t>biases</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Something else</t>
-        </is>
-      </c>
-      <c r="C16">
+          <t>Something else</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_types</t>
+          <t>detail_types</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">How the data were collected, and by whom</t>
-        </is>
-      </c>
-      <c r="C17">
+          <t>How the data were collected, and by whom</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_types</t>
+          <t>detail_types</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">The analyses conducted, and why</t>
-        </is>
-      </c>
-      <c r="C18">
+          <t>The analyses conducted, and why</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_types</t>
+          <t>detail_types</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outliers, and how they relate to the data's backstory</t>
-        </is>
-      </c>
-      <c r="C19">
+          <t>Outliers, and how they relate to the data's backstory</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_levels</t>
+          <t>detail_levels</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Light: the headline and a line of context</t>
-        </is>
-      </c>
-      <c r="C20">
+          <t>Light: the headline and a line of context</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_levels</t>
+          <t>detail_levels</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moderate: enough to trust the finding</t>
-        </is>
-      </c>
-      <c r="C21">
+          <t>Moderate: enough to trust the finding</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">detail_levels</t>
+          <t>detail_levels</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full: enough to replicate it</t>
-        </is>
-      </c>
-      <c r="C22">
+          <t>Full: enough to replicate it</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">arcs</t>
+          <t>arcs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data storytelling arc (the data's subjects are the main characters)</t>
-        </is>
-      </c>
-      <c r="C23">
+          <t>Data storytelling arc (the data's subjects are the main characters)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">arcs</t>
+          <t>arcs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research method arc (the method is the plot)</t>
-        </is>
-      </c>
-      <c r="C24">
+          <t>Research method arc (the method is the plot)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_types</t>
+          <t>illustration_types</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chart or graph</t>
-        </is>
-      </c>
-      <c r="C25">
+          <t>Chart or graph</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_types</t>
+          <t>illustration_types</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diagram or graphic</t>
-        </is>
-      </c>
-      <c r="C26">
+          <t>Diagram or graphic</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_types</t>
+          <t>illustration_types</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Table</t>
-        </is>
-      </c>
-      <c r="C27">
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_types</t>
+          <t>illustration_types</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Personal story or anecdote</t>
-        </is>
-      </c>
-      <c r="C28">
+          <t>Personal story or anecdote</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_types</t>
+          <t>illustration_types</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Something else</t>
-        </is>
-      </c>
-      <c r="C29">
+          <t>Something else</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_checks</t>
+          <t>illustration_checks</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decluttered it, so the key insight stands out</t>
-        </is>
-      </c>
-      <c r="C30">
+          <t>Decluttered it, so the key insight stands out</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_checks</t>
+          <t>illustration_checks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set a hierarchy, with color used on purpose to guide focus</t>
-        </is>
-      </c>
-      <c r="C31">
+          <t>Set a hierarchy, with color used on purpose to guide focus</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">illustration_checks</t>
+          <t>illustration_checks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Used text well: a concise title, clear labels, and annotations</t>
-        </is>
-      </c>
-      <c r="C32">
+          <t>Used text well: a concise title, clear labels, and annotations</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">cta_modes</t>
+          <t>cta_modes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direct: a specific action for the audience</t>
-        </is>
-      </c>
-      <c r="C33">
+          <t>Direct: a specific action for the audience</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">cta_modes</t>
+          <t>cta_modes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collective: the course of action is worked out with the audience</t>
-        </is>
-      </c>
-      <c r="C34">
+          <t>Collective: the course of action is worked out with the audience</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Website</t>
-        </is>
-      </c>
-      <c r="C35">
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Social media</t>
-        </is>
-      </c>
-      <c r="C36">
+          <t>Social media</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Community event</t>
-        </is>
-      </c>
-      <c r="C37">
+          <t>Community event</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newsletter</t>
-        </is>
-      </c>
-      <c r="C38">
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels</t>
+          <t>channels</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Something else</t>
-        </is>
-      </c>
-      <c r="C39">
+          <t>Something else</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">sustain</t>
+          <t>sustain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ongoing themes or characters</t>
-        </is>
-      </c>
-      <c r="C40">
+          <t>Ongoing themes or characters</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">sustain</t>
+          <t>sustain</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Timing it for when the audience is most ready</t>
-        </is>
-      </c>
-      <c r="C41">
+          <t>Timing it for when the audience is most ready</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">sustain</t>
+          <t>sustain</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tying it to broader, long-term court objectives</t>
-        </is>
-      </c>
-      <c r="C42">
+          <t>Tying it to broader, long-term court objectives</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">text</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">page_sub</t>
+          <t>page_sub</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan a data story, one element at a time.</t>
+          <t>Plan a data story, one element at a time.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro_eyebrow</t>
+          <t>intro_eyebrow</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Storytelling</t>
+          <t>Data Storytelling</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro_title</t>
+          <t>intro_title</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">A data story is planned long before it is written, and this is where the planning goes.</t>
+          <t>A data story is planned long before it is written, and this is where the planning goes.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro_lead</t>
+          <t>intro_lead</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Data STORY framework breaks a data story into five elements and seventeen steps, from the objective you start with to the response you measure at the end. Work through them in whatever order suits you, skip what does not apply yet, and leave with a one-page plan you can print or download.</t>
+          <t>The Data STORY framework breaks a data story into five elements and seventeen steps, from the objective you start with to the response you measure at the end. Work through them in whatever order suits you, skip what does not apply yet, and leave with a one-page plan you can print or download.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro_btn</t>
+          <t>intro_btn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start the worksheet</t>
+          <t>Start the worksheet</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro_note</t>
+          <t>intro_note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your answers stay in this browser. Nothing is sent anywhere, so it is safe to plan with real findings.</t>
+          <t>Your answers stay in this browser. Nothing is sent anywhere, so it is safe to plan with real findings.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">nav_label</t>
+          <t>nav_label</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">STORY elements</t>
+          <t>STORY elements</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">btn_plan</t>
+          <t>btn_plan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">See your plan</t>
+          <t>See your plan</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">btn_back</t>
+          <t>btn_back</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to the worksheet</t>
+          <t>Back to the worksheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">btn_print</t>
+          <t>btn_print</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Print</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">btn_docx</t>
+          <t>btn_docx</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Download as Word</t>
+          <t>Download as Word</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">btn_reset</t>
+          <t>btn_reset</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start over</t>
+          <t>Start over</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">confirm_reset</t>
+          <t>confirm_reset</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clear every answer on this worksheet? This cannot be undone.</t>
+          <t>Clear every answer on this worksheet? This cannot be undone.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">select_placeholder</t>
+          <t>select_placeholder</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Choose one</t>
+          <t>Choose one</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">progress</t>
+          <t>progress</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">{done} of {total} steps</t>
+          <t>{done} of {total} steps</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan_eyebrow</t>
+          <t>plan_eyebrow</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Your Data STORY</t>
+          <t>Your Data STORY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan_title</t>
+          <t>plan_title</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Story Plan</t>
+          <t>Story Plan</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan_lead</t>
+          <t>plan_lead</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Everything you entered, arranged by element and step. Blank steps are marked, so you can see what is left.</t>
+          <t>Everything you entered, arranged by element and step. Blank steps are marked, so you can see what is left.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan_unanswered</t>
+          <t>plan_unanswered</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not yet answered</t>
+          <t>Not yet answered</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan_date</t>
+          <t>plan_date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prepared {date}</t>
+          <t>Prepared {date}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">step_open</t>
+          <t>step_open</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step {n}</t>
+          <t>Step {n}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">saved_note</t>
+          <t>saved_note</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saved in this browser as you type.</t>
+          <t>Saved in this browser as you type.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">scope_note</t>
+          <t>scope_note</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">The worksheet plans a story; it does not write one. Treat the plan as a first draft to revise as the story takes shape, which is how storyboarding works.</t>
+          <t>The worksheet plans a story; it does not write one. Treat the plan as a first draft to revise as the story takes shape, which is how storyboarding works.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>